--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/mar-2025.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/mar-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC mar-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC mar-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11777,7 +11777,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12326,7 +12326,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13485,7 +13485,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14949,7 +14949,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15803,7 +15803,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15864,7 +15864,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16047,7 +16047,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16108,7 +16108,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16413,7 +16413,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17084,7 +17084,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17267,7 +17267,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17694,7 +17694,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17877,7 +17877,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18121,7 +18121,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18243,7 +18243,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18548,7 +18548,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18609,7 +18609,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18670,7 +18670,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18792,7 +18792,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18853,7 +18853,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -18975,7 +18975,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19341,7 +19341,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19402,7 +19402,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19585,7 +19585,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19707,7 +19707,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19768,7 +19768,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19890,7 +19890,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -19951,7 +19951,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20073,7 +20073,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20195,7 +20195,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20317,7 +20317,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20378,7 +20378,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20500,7 +20500,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20622,7 +20622,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -20683,7 +20683,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21049,7 +21049,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -21232,7 +21232,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21293,7 +21293,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21354,7 +21354,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21415,7 +21415,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21476,7 +21476,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21537,7 +21537,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21598,7 +21598,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21659,7 +21659,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21720,7 +21720,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21781,7 +21781,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -21964,7 +21964,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/mar-2025.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/mar-2025.xlsx
@@ -562,7 +562,11 @@
           <t>76.399.126-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1058,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1245,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1371,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1436,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1562,11 @@
           <t>77.831.852-0</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1814,11 @@
           <t>52.003.040-9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1847,7 +1879,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2066,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2375,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2440,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2566,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2631,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3184,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3310,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3372,7 +3436,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3684,11 @@
           <t>76.193.188-1</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4226,7 +4298,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4348,7 +4424,11 @@
           <t>77.721.515-9</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4714,7 +4794,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4836,7 +4920,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5019,7 +5107,11 @@
           <t>77.512.806-2</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5080,7 +5172,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5202,7 +5298,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5324,7 +5424,11 @@
           <t>77.163.858-9</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5385,7 +5489,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5507,7 +5615,11 @@
           <t>52.003.040-9</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5690,7 +5802,11 @@
           <t>52.003.040-9</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5812,7 +5928,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +5993,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6300,7 +6424,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6361,7 +6489,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6971,7 +7103,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7154,7 +7290,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7276,7 +7416,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7581,7 +7725,11 @@
           <t>77.352.453-K</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8252,7 +8400,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8313,7 +8465,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8374,7 +8530,11 @@
           <t>77.163.842-2</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8618,7 +8778,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8679,7 +8843,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9106,7 +9274,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9289,7 +9461,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9411,7 +9587,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9472,7 +9652,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9716,7 +9900,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10021,7 +10209,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10265,7 +10457,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10692,7 +10888,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10875,7 +11075,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11119,7 +11323,11 @@
           <t>77.575.038-3</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11485,7 +11693,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11546,7 +11758,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11607,7 +11823,11 @@
           <t>52.003.040-9</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11668,7 +11888,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11729,7 +11953,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11851,7 +12079,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11912,7 +12144,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12217,7 +12453,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12644,7 +12884,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12766,7 +13010,11 @@
           <t>52.003.040-9</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12888,7 +13136,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13498,7 +13750,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14047,7 +14303,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14291,7 +14551,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14840,7 +15104,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14962,7 +15230,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15023,7 +15295,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15145,7 +15421,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15511,7 +15791,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15633,7 +15917,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15816,7 +16104,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15938,7 +16230,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15999,7 +16295,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16121,7 +16421,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16609,7 +16913,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17524,7 +17832,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17585,7 +17897,11 @@
           <t>77.787.617-1</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18012,7 +18328,11 @@
           <t>77.163.842-2</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18317,7 +18637,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18439,7 +18763,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18622,7 +18950,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18866,7 +19198,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19232,7 +19568,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19293,7 +19633,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19415,7 +19759,11 @@
           <t>52.003.040-9</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19476,7 +19824,11 @@
           <t>77.163.858-9</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19598,7 +19950,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19720,7 +20076,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20391,7 +20751,11 @@
           <t>77.173.807-9</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20452,7 +20816,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20635,7 +21003,11 @@
           <t>77.787.617-1</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20696,7 +21068,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20818,7 +21194,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20940,7 +21320,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21977,7 +22361,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/mar-2025.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/mar-2025.xlsx
@@ -3749,7 +3749,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5554,7 +5558,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10644,7 +10652,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11571,7 +11583,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11632,7 +11648,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13445,7 +13465,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18828,7 +18852,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22239,7 +22267,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
